--- a/data/trans_bre/P2A_lim_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,31</t>
+          <t>-1,43; 3,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,96</t>
+          <t>-3,48; 3,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,71</t>
+          <t>1,14; 7,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 5,28</t>
+          <t>-3,35; 5,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 33,81</t>
+          <t>-11,5; 37,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 20,53</t>
+          <t>-19,87; 21,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,09; 82,01</t>
+          <t>8,33; 79,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 23,74</t>
+          <t>-11,55; 23,35</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,04</t>
+          <t>-1,18; 1,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 3,81</t>
+          <t>0,1; 3,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,7</t>
+          <t>-1,58; 1,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 33,83</t>
+          <t>-0,67; 33,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 49,89</t>
+          <t>-20,07; 47,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 57,14</t>
+          <t>1,43; 59,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 30,62</t>
+          <t>-22,26; 31,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 364,8</t>
+          <t>-5,85; 344,96</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,03</t>
+          <t>-0,61; 4,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 6,39</t>
+          <t>-0,66; 6,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,22</t>
+          <t>-2,01; 3,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 1,62</t>
+          <t>-4,75; 1,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 200,47</t>
+          <t>-13,54; 187,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 181,96</t>
+          <t>-11,81; 173,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 114,11</t>
+          <t>-37,86; 105,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,06; 24,45</t>
+          <t>-40,92; 21,06</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,69</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,5</t>
+          <t>0,45; 3,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,1</t>
+          <t>0,41; 3,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 19,82</t>
+          <t>0,51; 20,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 44,83</t>
+          <t>-0,0; 44,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 39,86</t>
+          <t>4,01; 40,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 49,46</t>
+          <t>5,09; 47,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 184,6</t>
+          <t>3,39; 166,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_lim_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,75</t>
+          <t>-1,67; 3,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,08</t>
+          <t>-3,35; 2,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,72</t>
+          <t>1,08; 7,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 5,27</t>
+          <t>-1,48; 6,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 37,6</t>
+          <t>-13,06; 35,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 21,18</t>
+          <t>-18,34; 19,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 79,94</t>
+          <t>8,93; 84,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 23,35</t>
+          <t>-5,46; 32,24</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>-2,06%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,98</t>
+          <t>-1,13; 1,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,94</t>
+          <t>0,05; 3,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,72</t>
+          <t>-1,49; 1,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 33,37</t>
+          <t>-2,16; 1,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 47,48</t>
+          <t>-20,34; 45,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 59,95</t>
+          <t>0,25; 60,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 31,8</t>
+          <t>-21,27; 30,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 344,96</t>
+          <t>-16,49; 16,77</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,36</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-14,8%</t>
+          <t>-13,34%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,7</t>
+          <t>-0,87; 4,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 6,75</t>
+          <t>-0,89; 6,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,13</t>
+          <t>-1,98; 3,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,55</t>
+          <t>-4,54; 1,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 187,16</t>
+          <t>-23,24; 192,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 173,42</t>
+          <t>-15,45; 183,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 105,81</t>
+          <t>-38,65; 131,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 21,06</t>
+          <t>-39,79; 23,72</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,96</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,15; 2,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,61</t>
+          <t>0,27; 3,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,02</t>
+          <t>0,32; 3,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 20,71</t>
+          <t>-0,6; 2,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 44,34</t>
+          <t>1,9; 45,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 40,86</t>
+          <t>2,37; 38,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 47,98</t>
+          <t>4,18; 48,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 166,28</t>
+          <t>-4,22; 19,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_lim_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
